--- a/Carpeta_N3_Base_de_datos_y_codigo/salidas/tabla5_vif_multicolinealidad.xlsx
+++ b/Carpeta_N3_Base_de_datos_y_codigo/salidas/tabla5_vif_multicolinealidad.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>
